--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.55447083888181</v>
+        <v>4.315101511318295</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41578578898229</v>
+        <v>3.155065190709623</v>
       </c>
       <c r="E2" t="n">
-        <v>8.628572649432973</v>
+        <v>1.402143055532858</v>
       </c>
       <c r="F2" t="n">
-        <v>11.41007040699905</v>
+        <v>1.854136441137346</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.38186702592222</v>
+        <v>4.449553391712361</v>
       </c>
       <c r="D3" t="n">
-        <v>38.16215904862232</v>
+        <v>6.201350845401127</v>
       </c>
       <c r="E3" t="n">
-        <v>8.628572649432973</v>
+        <v>1.402143055532858</v>
       </c>
       <c r="F3" t="n">
-        <v>11.41007040699905</v>
+        <v>1.854136441137346</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.03211018234018</v>
+        <v>5.367717904630279</v>
       </c>
       <c r="D4" t="n">
-        <v>48.99869463226338</v>
+        <v>7.962287877742799</v>
       </c>
       <c r="E4" t="n">
-        <v>8.628572649432973</v>
+        <v>1.402143055532858</v>
       </c>
       <c r="F4" t="n">
-        <v>11.41007040699905</v>
+        <v>1.854136441137346</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.84779549096589</v>
+        <v>5.987766767281958</v>
       </c>
       <c r="D5" t="n">
-        <v>23.24932004483641</v>
+        <v>3.778014507285916</v>
       </c>
       <c r="E5" t="n">
-        <v>8.628572649432973</v>
+        <v>1.402143055532858</v>
       </c>
       <c r="F5" t="n">
-        <v>11.41007040699905</v>
+        <v>1.854136441137346</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.55551143319371</v>
+        <v>8.215270607893979</v>
       </c>
       <c r="D6" t="n">
-        <v>22.15218162207245</v>
+        <v>3.599729513586773</v>
       </c>
       <c r="E6" t="n">
-        <v>8.628572649432973</v>
+        <v>1.402143055532858</v>
       </c>
       <c r="F6" t="n">
-        <v>11.41007040699905</v>
+        <v>1.854136441137346</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.36085378046473</v>
+        <v>3.796138739325519</v>
       </c>
       <c r="D7" t="n">
-        <v>43.52708553865093</v>
+        <v>7.073151400030777</v>
       </c>
       <c r="E7" t="n">
-        <v>8.628572649432973</v>
+        <v>1.402143055532858</v>
       </c>
       <c r="F7" t="n">
-        <v>11.41007040699905</v>
+        <v>1.854136441137346</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.08020441662664</v>
+        <v>6.350533217701829</v>
       </c>
       <c r="D8" t="n">
-        <v>44.49781517732703</v>
+        <v>7.230894966315642</v>
       </c>
       <c r="E8" t="n">
-        <v>8.628572649432973</v>
+        <v>1.402143055532858</v>
       </c>
       <c r="F8" t="n">
-        <v>11.41007040699905</v>
+        <v>1.854136441137346</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
